--- a/excel_files/16.2.2.xlsx
+++ b/excel_files/16.2.2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="91">
   <si>
     <t>Көрсөткүчтөрдүн аталышы</t>
   </si>
@@ -296,7 +296,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -391,6 +391,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -446,7 +475,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -573,6 +602,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -879,7 +923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="37.140625" customWidth="1"/>
@@ -887,7 +931,7 @@
     <col min="7" max="12" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="42" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" s="42" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>36</v>
       </c>
@@ -912,7 +956,7 @@
       <c r="P1" s="41"/>
       <c r="Q1" s="41"/>
     </row>
-    <row r="2" spans="1:17" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>34</v>
       </c>
@@ -937,7 +981,7 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="35"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -956,7 +1000,7 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
@@ -1008,8 +1052,11 @@
       <c r="Q4" s="22">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R4" s="47">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>37</v>
       </c>
@@ -1076,7 +1123,7 @@
         <v>0.23736684767052366</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="8" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" s="8" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="43" t="s">
         <v>90</v>
       </c>
@@ -1128,8 +1175,11 @@
       <c r="Q6" s="25">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R6" s="48">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>85</v>
       </c>
@@ -1182,7 +1232,7 @@
         <v>7161910</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>54</v>
       </c>
@@ -1206,8 +1256,9 @@
       <c r="O8" s="28"/>
       <c r="P8" s="28"/>
       <c r="Q8" s="28"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R8" s="49"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>56</v>
       </c>
@@ -1259,8 +1310,11 @@
       <c r="Q9" s="28">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R9" s="50">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>57</v>
       </c>
@@ -1310,8 +1364,11 @@
       <c r="Q10" s="28">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R10" s="50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>60</v>
       </c>
@@ -1363,8 +1420,11 @@
       <c r="Q11" s="29" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R11" s="50" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>63</v>
       </c>
@@ -1388,8 +1448,9 @@
       <c r="O12" s="32"/>
       <c r="P12" s="32"/>
       <c r="Q12" s="32"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R12" s="49"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
@@ -1441,8 +1502,11 @@
       <c r="Q13" s="29" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R13" s="50" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
@@ -1490,8 +1554,11 @@
       <c r="Q14" s="29" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R14" s="50" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>16</v>
       </c>
@@ -1543,8 +1610,11 @@
       <c r="Q15" s="29" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R15" s="50" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>19</v>
       </c>
@@ -1596,8 +1666,11 @@
       <c r="Q16" s="29" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R16" s="50" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>21</v>
       </c>
@@ -1643,8 +1716,11 @@
       <c r="O17" s="29"/>
       <c r="P17" s="29"/>
       <c r="Q17" s="29"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R17" s="49" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>23</v>
       </c>
@@ -1696,8 +1772,11 @@
       <c r="Q18" s="29" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R18" s="50" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>25</v>
       </c>
@@ -1749,8 +1828,11 @@
       <c r="Q19" s="29">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R19" s="49" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>27</v>
       </c>
@@ -1802,8 +1884,11 @@
       <c r="Q20" s="29">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R20" s="49">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>29</v>
       </c>
@@ -1855,8 +1940,11 @@
       <c r="Q21" s="29" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R21" s="49" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>65</v>
       </c>
@@ -1880,8 +1968,9 @@
       <c r="O22" s="36"/>
       <c r="P22" s="36"/>
       <c r="Q22" s="36"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R22" s="51"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>72</v>
       </c>
@@ -1933,8 +2022,11 @@
       <c r="Q23" s="37">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R23" s="52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>73</v>
       </c>
@@ -1984,8 +2076,11 @@
       <c r="Q24" s="29">
         <v>12</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R24" s="52">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>74</v>
       </c>
@@ -2037,8 +2132,11 @@
       <c r="Q25" s="37" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R25" s="52">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>75</v>
       </c>
@@ -2090,8 +2188,11 @@
       <c r="Q26" s="37" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R26" s="52" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>76</v>
       </c>
@@ -2143,8 +2244,11 @@
       <c r="Q27" s="37" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R27" s="52" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="44" t="s">
         <v>84</v>
       </c>
@@ -2168,8 +2272,9 @@
       <c r="O28" s="38"/>
       <c r="P28" s="38"/>
       <c r="Q28" s="38"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R28" s="52"/>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="45" t="s">
         <v>77</v>
       </c>
@@ -2221,8 +2326,11 @@
       <c r="Q29" s="37">
         <v>13</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R29" s="52">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="45" t="s">
         <v>78</v>
       </c>
@@ -2274,8 +2382,11 @@
       <c r="Q30" s="37" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R30" s="52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="46" t="s">
         <v>83</v>
       </c>
@@ -2325,6 +2436,9 @@
         <v>3</v>
       </c>
       <c r="Q31" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="R31" s="53" t="s">
         <v>3</v>
       </c>
     </row>

--- a/excel_files/16.2.2.xlsx
+++ b/excel_files/16.2.2.xlsx
@@ -1,20 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6925AF-7229-4342-A76E-80CDFB199899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="91">
   <si>
     <t>Көрсөткүчтөрдүн аталышы</t>
   </si>
@@ -292,7 +304,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -475,7 +487,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -491,90 +503,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -591,37 +544,43 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 6" xfId="1"/>
+    <cellStyle name="Обычный 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -637,9 +596,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -677,9 +636,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -714,7 +673,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -749,7 +708,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -922,8 +881,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="37.140625" customWidth="1"/>
@@ -931,44 +890,44 @@
     <col min="7" max="12" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="42" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:19" s="21" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-    </row>
-    <row r="2" spans="1:18" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+    </row>
+    <row r="2" spans="1:19" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -981,8 +940,8 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
     </row>
-    <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="35"/>
+    <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -1000,63 +959,66 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+    <row r="4" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="21" t="s">
+      <c r="B4" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="15">
         <v>2010</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="15">
         <v>2011</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="15">
         <v>2012</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="15">
         <v>2013</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="15">
         <v>2014</v>
       </c>
-      <c r="I4" s="23">
+      <c r="I4" s="15">
         <v>2015</v>
       </c>
-      <c r="J4" s="22">
+      <c r="J4" s="15">
         <v>2016</v>
       </c>
-      <c r="K4" s="22">
+      <c r="K4" s="15">
         <v>2017</v>
       </c>
-      <c r="L4" s="22">
+      <c r="L4" s="15">
         <v>2018</v>
       </c>
-      <c r="M4" s="22">
+      <c r="M4" s="15">
         <v>2019</v>
       </c>
-      <c r="N4" s="22">
+      <c r="N4" s="15">
         <v>2020</v>
       </c>
-      <c r="O4" s="22">
+      <c r="O4" s="15">
         <v>2021</v>
       </c>
-      <c r="P4" s="22">
+      <c r="P4" s="15">
         <v>2022</v>
       </c>
-      <c r="Q4" s="22">
+      <c r="Q4" s="15">
         <v>2023</v>
       </c>
-      <c r="R4" s="47">
+      <c r="R4" s="22">
         <v>2024</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S4" s="22">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>37</v>
       </c>
@@ -1066,199 +1028,215 @@
       <c r="C5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="27">
         <f t="shared" ref="D5:Q5" si="0">D6/D7*100000</f>
         <v>0.38160406724517842</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="27">
         <f t="shared" si="0"/>
         <v>8.9444046219674223E-2</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="27">
         <f t="shared" si="0"/>
         <v>0.10500405578165456</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="27">
         <f t="shared" si="0"/>
         <v>0.15410338796298437</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="27">
         <f t="shared" si="0"/>
         <v>0.31818014354948371</v>
       </c>
-      <c r="I5" s="24">
+      <c r="I5" s="27">
         <f t="shared" si="0"/>
         <v>0.13096266892751887</v>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="27">
         <f t="shared" si="0"/>
         <v>0.16020341989444517</v>
       </c>
-      <c r="K5" s="24">
+      <c r="K5" s="27">
         <f t="shared" si="0"/>
         <v>7.8476587373399603E-2</v>
       </c>
-      <c r="L5" s="24">
+      <c r="L5" s="27">
         <f t="shared" si="0"/>
         <v>0.10741418757279229</v>
       </c>
-      <c r="M5" s="24">
+      <c r="M5" s="27">
         <f t="shared" si="0"/>
         <v>0.16507613311259153</v>
       </c>
-      <c r="N5" s="24">
+      <c r="N5" s="27">
         <f t="shared" si="0"/>
         <v>0.13255569290616426</v>
       </c>
-      <c r="O5" s="24">
+      <c r="O5" s="27">
         <f t="shared" si="0"/>
         <v>8.6794894550712737E-2</v>
       </c>
-      <c r="P5" s="24">
+      <c r="P5" s="27">
         <f t="shared" si="0"/>
         <v>4.2628229265984523E-2</v>
       </c>
-      <c r="Q5" s="24">
+      <c r="Q5" s="27">
         <f t="shared" si="0"/>
         <v>0.23736684767052366</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" s="8" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="43" t="s">
+      <c r="R5" s="27">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="S5" s="27">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" s="1" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="29">
         <v>21</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="29">
         <v>5</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="29">
         <v>6</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="29">
         <v>9</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="29">
         <v>19</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="29">
         <v>8</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="29">
         <v>10</v>
       </c>
-      <c r="K6" s="25">
+      <c r="K6" s="29">
         <v>5</v>
       </c>
-      <c r="L6" s="25">
+      <c r="L6" s="29">
         <v>7</v>
       </c>
-      <c r="M6" s="25">
+      <c r="M6" s="29">
         <v>11</v>
       </c>
-      <c r="N6" s="25">
+      <c r="N6" s="29">
         <v>9</v>
       </c>
-      <c r="O6" s="25">
+      <c r="O6" s="29">
         <v>6</v>
       </c>
-      <c r="P6" s="25">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="25">
+      <c r="P6" s="29">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="29">
         <v>17</v>
       </c>
-      <c r="R6" s="48">
+      <c r="R6" s="30">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="S6" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="16">
         <v>5503086</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="16">
         <v>5590087</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="16">
         <v>5714065</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="16">
         <v>5840235</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="16">
         <v>5971460</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="16">
         <v>6108611</v>
       </c>
-      <c r="J7" s="27">
+      <c r="J7" s="16">
         <v>6242064</v>
       </c>
-      <c r="K7" s="27">
+      <c r="K7" s="16">
         <v>6371327</v>
       </c>
-      <c r="L7" s="27">
+      <c r="L7" s="16">
         <v>6516830</v>
       </c>
-      <c r="M7" s="28">
+      <c r="M7" s="16">
         <v>6663592</v>
       </c>
-      <c r="N7" s="28">
+      <c r="N7" s="16">
         <v>6789599</v>
       </c>
-      <c r="O7" s="28">
+      <c r="O7" s="16">
         <v>6912849</v>
       </c>
-      <c r="P7" s="28">
+      <c r="P7" s="16">
         <v>7037590</v>
       </c>
-      <c r="Q7" s="28">
+      <c r="Q7" s="16">
         <v>7161910</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="R7" s="16">
+        <v>7281827</v>
+      </c>
+      <c r="S7" s="16">
+        <v>7404329</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="49"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="31"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>56</v>
       </c>
@@ -1268,189 +1246,197 @@
       <c r="C9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="27">
-        <v>1</v>
-      </c>
-      <c r="M9" s="28">
-        <v>1</v>
-      </c>
-      <c r="N9" s="28">
+      <c r="D9" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="16">
+        <v>1</v>
+      </c>
+      <c r="M9" s="16">
+        <v>1</v>
+      </c>
+      <c r="N9" s="16">
         <v>4</v>
       </c>
-      <c r="O9" s="28">
-        <v>1</v>
-      </c>
-      <c r="P9" s="28">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="28">
+      <c r="O9" s="16">
+        <v>1</v>
+      </c>
+      <c r="P9" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="16">
         <v>13</v>
       </c>
-      <c r="R9" s="50">
+      <c r="R9" s="23">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S9" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="27">
-        <v>3</v>
-      </c>
-      <c r="M10" s="28">
+      <c r="D10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="16">
+        <v>3</v>
+      </c>
+      <c r="M10" s="16">
         <v>6</v>
       </c>
-      <c r="N10" s="28"/>
-      <c r="O10" s="28">
+      <c r="N10" s="16"/>
+      <c r="O10" s="16">
         <v>4</v>
       </c>
-      <c r="P10" s="28">
+      <c r="P10" s="16">
         <v>2</v>
       </c>
-      <c r="Q10" s="28">
+      <c r="Q10" s="16">
         <v>4</v>
       </c>
-      <c r="R10" s="50">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R10" s="23">
+        <v>3</v>
+      </c>
+      <c r="S10" s="31"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="4" t="s">
         <v>61</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="F11" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="G11" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="H11" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="I11" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="J11" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="K11" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="L11" s="27">
-        <v>3</v>
-      </c>
-      <c r="M11" s="29">
+      <c r="D11" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L11" s="16">
+        <v>3</v>
+      </c>
+      <c r="M11" s="16">
         <v>4</v>
       </c>
-      <c r="N11" s="29">
+      <c r="N11" s="16">
         <v>5</v>
       </c>
-      <c r="O11" s="29">
-        <v>1</v>
-      </c>
-      <c r="P11" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q11" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="R11" s="50" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+      <c r="O11" s="16">
+        <v>1</v>
+      </c>
+      <c r="P11" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="R11" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="S11" s="23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="32"/>
-      <c r="N12" s="32"/>
-      <c r="O12" s="32"/>
-      <c r="P12" s="32"/>
-      <c r="Q12" s="32"/>
-      <c r="R12" s="49"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="23"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
@@ -1460,53 +1446,56 @@
       <c r="C13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="28">
-        <v>1</v>
-      </c>
-      <c r="G13" s="28">
+      <c r="D13" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="16">
+        <v>1</v>
+      </c>
+      <c r="G13" s="16">
         <v>2</v>
       </c>
-      <c r="H13" s="28">
-        <v>1</v>
-      </c>
-      <c r="I13" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="J13" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="K13" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="L13" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="M13" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="N13" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="O13" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="P13" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="R13" s="50" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H13" s="16">
+        <v>1</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="N13" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="O13" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="P13" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="R13" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="S13" s="23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
@@ -1516,49 +1505,52 @@
       <c r="C14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="29">
-        <v>1</v>
-      </c>
-      <c r="H14" s="29">
-        <v>1</v>
-      </c>
-      <c r="I14" s="29">
-        <v>1</v>
-      </c>
-      <c r="J14" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29">
-        <v>1</v>
-      </c>
-      <c r="P14" s="29">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="50" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D14" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="16">
+        <v>1</v>
+      </c>
+      <c r="H14" s="16">
+        <v>1</v>
+      </c>
+      <c r="I14" s="16">
+        <v>1</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16">
+        <v>1</v>
+      </c>
+      <c r="P14" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>16</v>
       </c>
@@ -1568,53 +1560,56 @@
       <c r="C15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="29">
-        <v>1</v>
-      </c>
-      <c r="H15" s="29">
-        <v>1</v>
-      </c>
-      <c r="I15" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="K15" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="M15" s="29">
-        <v>1</v>
-      </c>
-      <c r="N15" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="P15" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="R15" s="50" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D15" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="16">
+        <v>1</v>
+      </c>
+      <c r="H15" s="16">
+        <v>1</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="16">
+        <v>1</v>
+      </c>
+      <c r="N15" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>19</v>
       </c>
@@ -1624,53 +1619,56 @@
       <c r="C16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="F16" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G16" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="H16" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="I16" s="29">
-        <v>1</v>
-      </c>
-      <c r="J16" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="K16" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="L16" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="M16" s="29">
-        <v>1</v>
-      </c>
-      <c r="N16" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="O16" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="P16" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q16" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="R16" s="50" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D16" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" s="16">
+        <v>1</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="M16" s="16">
+        <v>1</v>
+      </c>
+      <c r="N16" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="O16" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="P16" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="R16" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="S16" s="23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>21</v>
       </c>
@@ -1680,47 +1678,50 @@
       <c r="C17" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="16">
         <v>5</v>
       </c>
-      <c r="E17" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="F17" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" s="29">
-        <v>1</v>
-      </c>
-      <c r="H17" s="29">
+      <c r="E17" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="16">
+        <v>1</v>
+      </c>
+      <c r="H17" s="16">
         <v>6</v>
       </c>
-      <c r="I17" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="29">
+      <c r="I17" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" s="16">
         <v>2</v>
       </c>
-      <c r="L17" s="29">
-        <v>1</v>
-      </c>
-      <c r="M17" s="29">
+      <c r="L17" s="16">
+        <v>1</v>
+      </c>
+      <c r="M17" s="16">
         <v>2</v>
       </c>
-      <c r="N17" s="29">
-        <v>1</v>
-      </c>
-      <c r="O17" s="29"/>
-      <c r="P17" s="29"/>
-      <c r="Q17" s="29"/>
-      <c r="R17" s="49" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="N17" s="16">
+        <v>1</v>
+      </c>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>23</v>
       </c>
@@ -1730,53 +1731,56 @@
       <c r="C18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="F18" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G18" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="50" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>25</v>
       </c>
@@ -1786,53 +1790,56 @@
       <c r="C19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="16">
         <v>2</v>
       </c>
-      <c r="E19" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="F19" s="28">
+      <c r="E19" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" s="16">
         <v>2</v>
       </c>
-      <c r="G19" s="28">
-        <v>3</v>
-      </c>
-      <c r="H19" s="28">
-        <v>3</v>
-      </c>
-      <c r="I19" s="28">
-        <v>3</v>
-      </c>
-      <c r="J19" s="28">
+      <c r="G19" s="16">
+        <v>3</v>
+      </c>
+      <c r="H19" s="16">
+        <v>3</v>
+      </c>
+      <c r="I19" s="16">
+        <v>3</v>
+      </c>
+      <c r="J19" s="16">
         <v>6</v>
       </c>
-      <c r="K19" s="28">
-        <v>3</v>
-      </c>
-      <c r="L19" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="M19" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="N19" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="O19" s="29">
+      <c r="K19" s="16">
+        <v>3</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="N19" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="O19" s="16">
         <v>2</v>
       </c>
-      <c r="P19" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q19" s="29">
+      <c r="P19" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q19" s="16">
         <v>15</v>
       </c>
-      <c r="R19" s="49" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R19" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="S19" s="23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>27</v>
       </c>
@@ -1842,552 +1849,581 @@
       <c r="C20" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="28">
-        <v>1</v>
-      </c>
-      <c r="E20" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="29">
-        <v>3</v>
-      </c>
-      <c r="G20" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="29">
+      <c r="D20" s="16">
+        <v>1</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="16">
+        <v>3</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="16">
         <v>2</v>
       </c>
-      <c r="I20" s="29">
-        <v>1</v>
-      </c>
-      <c r="J20" s="29">
+      <c r="I20" s="16">
+        <v>1</v>
+      </c>
+      <c r="J20" s="16">
         <v>4</v>
       </c>
-      <c r="K20" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="29">
+      <c r="K20" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="16">
         <v>6</v>
       </c>
-      <c r="M20" s="29">
+      <c r="M20" s="16">
         <v>5</v>
       </c>
-      <c r="N20" s="29">
+      <c r="N20" s="16">
         <v>8</v>
       </c>
-      <c r="O20" s="29">
-        <v>3</v>
-      </c>
-      <c r="P20" s="29">
+      <c r="O20" s="16">
+        <v>3</v>
+      </c>
+      <c r="P20" s="16">
         <v>2</v>
       </c>
-      <c r="Q20" s="29">
+      <c r="Q20" s="16">
         <v>2</v>
       </c>
-      <c r="R20" s="49">
+      <c r="R20" s="23">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="S20" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="16">
         <v>13</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="16">
         <v>5</v>
       </c>
-      <c r="F21" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="34">
-        <v>1</v>
-      </c>
-      <c r="H21" s="34">
+      <c r="F21" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="16">
+        <v>1</v>
+      </c>
+      <c r="H21" s="16">
         <v>5</v>
       </c>
-      <c r="I21" s="34">
+      <c r="I21" s="16">
         <v>2</v>
       </c>
-      <c r="J21" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="29">
+      <c r="J21" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="16">
         <v>2</v>
       </c>
-      <c r="N21" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="49" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="N21" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="51"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="24"/>
+      <c r="S22" s="32"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F23" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="G23" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="H23" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="37">
+      <c r="D23" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="16">
         <v>7</v>
       </c>
-      <c r="M23" s="37">
+      <c r="M23" s="16">
         <v>8</v>
       </c>
-      <c r="N23" s="37">
+      <c r="N23" s="16">
         <v>5</v>
       </c>
-      <c r="O23" s="37">
-        <v>1</v>
-      </c>
-      <c r="P23" s="37">
+      <c r="O23" s="16">
+        <v>1</v>
+      </c>
+      <c r="P23" s="16">
         <v>2</v>
       </c>
-      <c r="Q23" s="37">
+      <c r="Q23" s="16">
         <v>5</v>
       </c>
-      <c r="R23" s="52">
+      <c r="R23" s="24">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S23" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="29">
-        <v>1</v>
-      </c>
-      <c r="N24" s="37"/>
-      <c r="O24" s="29">
+      <c r="D24" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="16">
+        <v>1</v>
+      </c>
+      <c r="N24" s="16"/>
+      <c r="O24" s="16">
         <v>4</v>
       </c>
-      <c r="P24" s="37">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="29">
+      <c r="P24" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="16">
         <v>12</v>
       </c>
-      <c r="R24" s="52">
+      <c r="R24" s="24">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S24" s="24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="E25" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F25" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="G25" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="H25" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="I25" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="J25" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="K25" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="L25" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="M25" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="N25" s="37">
-        <v>3</v>
-      </c>
-      <c r="O25" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="P25" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q25" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="R25" s="52">
+      <c r="D25" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J25" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="N25" s="16">
+        <v>3</v>
+      </c>
+      <c r="O25" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="P25" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q25" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="R25" s="24">
         <v>8</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S25" s="24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D26" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="E26" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F26" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="G26" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="H26" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="52" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D27" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F27" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="G27" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="H27" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="52" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="44" t="s">
+      <c r="D27" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
-      <c r="O28" s="38"/>
-      <c r="P28" s="38"/>
-      <c r="Q28" s="38"/>
-      <c r="R28" s="52"/>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" s="45" t="s">
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="24"/>
+      <c r="S28" s="32"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D29" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="J29" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="K29" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="M29" s="37">
-        <v>1</v>
-      </c>
-      <c r="N29" s="37">
-        <v>3</v>
-      </c>
-      <c r="O29" s="37">
-        <v>1</v>
-      </c>
-      <c r="P29" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q29" s="37">
+      <c r="D29" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="M29" s="16">
+        <v>1</v>
+      </c>
+      <c r="N29" s="16">
+        <v>3</v>
+      </c>
+      <c r="O29" s="16">
+        <v>1</v>
+      </c>
+      <c r="P29" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="16">
         <v>13</v>
       </c>
-      <c r="R29" s="52">
+      <c r="R29" s="24">
         <v>17</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" s="45" t="s">
+      <c r="S29" s="24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D30" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="E30" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F30" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="G30" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="H30" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="I30" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="J30" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="K30" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="L30" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="M30" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="N30" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="O30" s="37">
+      <c r="D30" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J30" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="N30" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="O30" s="16">
         <v>2</v>
       </c>
-      <c r="P30" s="37">
-        <v>1</v>
-      </c>
-      <c r="Q30" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="R30" s="52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+      <c r="P30" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="R30" s="24">
+        <v>1</v>
+      </c>
+      <c r="S30" s="24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B31" s="5" t="s">
@@ -2396,49 +2432,52 @@
       <c r="C31" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="E31" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="F31" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="G31" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="H31" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="I31" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="J31" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="K31" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="L31" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="M31" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="N31" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="O31" s="39">
+      <c r="D31" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="H31" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="I31" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="J31" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="K31" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="L31" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="M31" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="N31" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="O31" s="18">
         <v>2</v>
       </c>
-      <c r="P31" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q31" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="R31" s="53" t="s">
+      <c r="P31" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="R31" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="S31" s="25" t="s">
         <v>3</v>
       </c>
     </row>
